--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_07-05-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_07-05-2026.xlsx
@@ -2336,7 +2336,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>£79.58</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
